--- a/artfynd/A 10862-2023 artfynd.xlsx
+++ b/artfynd/A 10862-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10862-2023 artfynd.xlsx
+++ b/artfynd/A 10862-2023 artfynd.xlsx
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119719046</v>
+        <v>119719056</v>
       </c>
       <c r="B10" t="n">
-        <v>56514</v>
+        <v>91840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,42 +1518,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701374</v>
+        <v>701769</v>
       </c>
       <c r="R10" t="n">
-        <v>7155505</v>
+        <v>7154938</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119719056</v>
+        <v>119719046</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>56514</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,38 +1620,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701769</v>
+        <v>701374</v>
       </c>
       <c r="R11" t="n">
-        <v>7154938</v>
+        <v>7155505</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 10862-2023 artfynd.xlsx
+++ b/artfynd/A 10862-2023 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119719031</v>
+        <v>119719057</v>
       </c>
       <c r="B3" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701907</v>
+        <v>701443</v>
       </c>
       <c r="R3" t="n">
-        <v>7154864</v>
+        <v>7155186</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119719037</v>
+        <v>119719043</v>
       </c>
       <c r="B4" t="n">
-        <v>91844</v>
+        <v>92030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,25 +906,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4365</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701483</v>
+        <v>701907</v>
       </c>
       <c r="R4" t="n">
-        <v>7155112</v>
+        <v>7154864</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119719045</v>
+        <v>119719039</v>
       </c>
       <c r="B5" t="n">
-        <v>91863</v>
+        <v>91856</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701467</v>
+        <v>701788</v>
       </c>
       <c r="R5" t="n">
-        <v>7155124</v>
+        <v>7154913</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119719041</v>
+        <v>119719045</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>91863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>702065</v>
+        <v>701467</v>
       </c>
       <c r="R6" t="n">
-        <v>7154717</v>
+        <v>7155124</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119719057</v>
+        <v>119719056</v>
       </c>
       <c r="B7" t="n">
         <v>91840</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701443</v>
+        <v>701769</v>
       </c>
       <c r="R7" t="n">
-        <v>7155186</v>
+        <v>7154938</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119719034</v>
+        <v>119719041</v>
       </c>
       <c r="B8" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,25 +1314,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701751</v>
+        <v>702065</v>
       </c>
       <c r="R8" t="n">
-        <v>7154965</v>
+        <v>7154717</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119719043</v>
+        <v>119719034</v>
       </c>
       <c r="B9" t="n">
-        <v>92030</v>
+        <v>91884</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701907</v>
+        <v>701751</v>
       </c>
       <c r="R9" t="n">
-        <v>7154864</v>
+        <v>7154965</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119719056</v>
+        <v>119719046</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>56514</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,38 +1518,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701769</v>
+        <v>701374</v>
       </c>
       <c r="R10" t="n">
-        <v>7154938</v>
+        <v>7155505</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119719046</v>
+        <v>119719037</v>
       </c>
       <c r="B11" t="n">
-        <v>56514</v>
+        <v>91844</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,42 +1624,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701374</v>
+        <v>701483</v>
       </c>
       <c r="R11" t="n">
-        <v>7155505</v>
+        <v>7155112</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,10 +1714,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119719039</v>
+        <v>119719031</v>
       </c>
       <c r="B12" t="n">
-        <v>91856</v>
+        <v>89633</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,21 +1730,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701788</v>
+        <v>701907</v>
       </c>
       <c r="R12" t="n">
-        <v>7154913</v>
+        <v>7154864</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 10862-2023 artfynd.xlsx
+++ b/artfynd/A 10862-2023 artfynd.xlsx
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119719056</v>
+        <v>119719041</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701769</v>
+        <v>702065</v>
       </c>
       <c r="R7" t="n">
-        <v>7154938</v>
+        <v>7154717</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119719041</v>
+        <v>119719056</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>702065</v>
+        <v>701769</v>
       </c>
       <c r="R8" t="n">
-        <v>7154717</v>
+        <v>7154938</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 10862-2023 artfynd.xlsx
+++ b/artfynd/A 10862-2023 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119719057</v>
+        <v>119719046</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>56514</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +804,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701443</v>
+        <v>701374</v>
       </c>
       <c r="R3" t="n">
-        <v>7155186</v>
+        <v>7155505</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119719043</v>
+        <v>119719056</v>
       </c>
       <c r="B4" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,25 +910,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701907</v>
+        <v>701769</v>
       </c>
       <c r="R4" t="n">
-        <v>7154864</v>
+        <v>7154938</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119719039</v>
+        <v>119719041</v>
       </c>
       <c r="B5" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +1012,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701788</v>
+        <v>702065</v>
       </c>
       <c r="R5" t="n">
-        <v>7154913</v>
+        <v>7154717</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119719045</v>
+        <v>119719039</v>
       </c>
       <c r="B6" t="n">
-        <v>91863</v>
+        <v>91856</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1118,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701467</v>
+        <v>701788</v>
       </c>
       <c r="R6" t="n">
-        <v>7155124</v>
+        <v>7154913</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119719041</v>
+        <v>119719037</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>91844</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1216,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>702065</v>
+        <v>701483</v>
       </c>
       <c r="R7" t="n">
-        <v>7154717</v>
+        <v>7155112</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119719056</v>
+        <v>119719043</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,25 +1318,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701769</v>
+        <v>701907</v>
       </c>
       <c r="R8" t="n">
-        <v>7154938</v>
+        <v>7154864</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119719034</v>
+        <v>119719031</v>
       </c>
       <c r="B9" t="n">
-        <v>91884</v>
+        <v>89633</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1424,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701751</v>
+        <v>701907</v>
       </c>
       <c r="R9" t="n">
-        <v>7154965</v>
+        <v>7154864</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119719046</v>
+        <v>119719045</v>
       </c>
       <c r="B10" t="n">
-        <v>56514</v>
+        <v>91863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,38 +1526,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701374</v>
+        <v>701467</v>
       </c>
       <c r="R10" t="n">
-        <v>7155505</v>
+        <v>7155124</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119719037</v>
+        <v>119719057</v>
       </c>
       <c r="B11" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,25 +1624,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701483</v>
+        <v>701443</v>
       </c>
       <c r="R11" t="n">
-        <v>7155112</v>
+        <v>7155186</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,10 +1714,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119719031</v>
+        <v>119719034</v>
       </c>
       <c r="B12" t="n">
-        <v>89633</v>
+        <v>91884</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,21 +1730,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701907</v>
+        <v>701751</v>
       </c>
       <c r="R12" t="n">
-        <v>7154864</v>
+        <v>7154965</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 10862-2023 artfynd.xlsx
+++ b/artfynd/A 10862-2023 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119719046</v>
+        <v>119719037</v>
       </c>
       <c r="B3" t="n">
-        <v>56514</v>
+        <v>91844</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,42 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>4365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701374</v>
+        <v>701483</v>
       </c>
       <c r="R3" t="n">
-        <v>7155505</v>
+        <v>7155112</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119719056</v>
+        <v>119719057</v>
       </c>
       <c r="B4" t="n">
         <v>91840</v>
@@ -938,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701769</v>
+        <v>701443</v>
       </c>
       <c r="R4" t="n">
-        <v>7154938</v>
+        <v>7155186</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119719041</v>
+        <v>119719031</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>89633</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>702065</v>
+        <v>701907</v>
       </c>
       <c r="R5" t="n">
-        <v>7154717</v>
+        <v>7154864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119719039</v>
+        <v>119719043</v>
       </c>
       <c r="B6" t="n">
-        <v>91856</v>
+        <v>92030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701788</v>
+        <v>701907</v>
       </c>
       <c r="R6" t="n">
-        <v>7154913</v>
+        <v>7154864</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119719037</v>
+        <v>119719056</v>
       </c>
       <c r="B7" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1244,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701483</v>
+        <v>701769</v>
       </c>
       <c r="R7" t="n">
-        <v>7155112</v>
+        <v>7154938</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119719043</v>
+        <v>119719034</v>
       </c>
       <c r="B8" t="n">
-        <v>92030</v>
+        <v>91884</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701907</v>
+        <v>701751</v>
       </c>
       <c r="R8" t="n">
-        <v>7154864</v>
+        <v>7154965</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119719031</v>
+        <v>119719045</v>
       </c>
       <c r="B9" t="n">
-        <v>89633</v>
+        <v>91863</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1448,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701907</v>
+        <v>701467</v>
       </c>
       <c r="R9" t="n">
-        <v>7154864</v>
+        <v>7155124</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119719045</v>
+        <v>119719046</v>
       </c>
       <c r="B10" t="n">
-        <v>91863</v>
+        <v>56514</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,34 +1522,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701467</v>
+        <v>701374</v>
       </c>
       <c r="R10" t="n">
-        <v>7155124</v>
+        <v>7155505</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119719057</v>
+        <v>119719041</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,21 +1628,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701443</v>
+        <v>702065</v>
       </c>
       <c r="R11" t="n">
-        <v>7155186</v>
+        <v>7154717</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,10 +1714,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119719034</v>
+        <v>119719039</v>
       </c>
       <c r="B12" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,21 +1730,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701751</v>
+        <v>701788</v>
       </c>
       <c r="R12" t="n">
-        <v>7154965</v>
+        <v>7154913</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 10862-2023 artfynd.xlsx
+++ b/artfynd/A 10862-2023 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119719037</v>
+        <v>119719045</v>
       </c>
       <c r="B3" t="n">
-        <v>91844</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701483</v>
+        <v>701467</v>
       </c>
       <c r="R3" t="n">
-        <v>7155112</v>
+        <v>7155124</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119719057</v>
+        <v>119719041</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>91870</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>701443</v>
+        <v>702065</v>
       </c>
       <c r="R4" t="n">
-        <v>7155186</v>
+        <v>7154717</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>119719031</v>
       </c>
       <c r="B5" t="n">
-        <v>89633</v>
+        <v>89650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119719043</v>
+        <v>119719057</v>
       </c>
       <c r="B6" t="n">
-        <v>92030</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701907</v>
+        <v>701443</v>
       </c>
       <c r="R6" t="n">
-        <v>7154864</v>
+        <v>7155186</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119719056</v>
+        <v>119719046</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>56524</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,38 +1212,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701769</v>
+        <v>701374</v>
       </c>
       <c r="R7" t="n">
-        <v>7154938</v>
+        <v>7155505</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1309,7 @@
         <v>119719034</v>
       </c>
       <c r="B8" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119719045</v>
+        <v>119719043</v>
       </c>
       <c r="B9" t="n">
-        <v>91863</v>
+        <v>92048</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1424,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701467</v>
+        <v>701907</v>
       </c>
       <c r="R9" t="n">
-        <v>7155124</v>
+        <v>7154864</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119719046</v>
+        <v>119719039</v>
       </c>
       <c r="B10" t="n">
-        <v>56514</v>
+        <v>91874</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,38 +1526,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701374</v>
+        <v>701788</v>
       </c>
       <c r="R10" t="n">
-        <v>7155505</v>
+        <v>7154913</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119719041</v>
+        <v>119719056</v>
       </c>
       <c r="B11" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,21 +1628,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>702065</v>
+        <v>701769</v>
       </c>
       <c r="R11" t="n">
-        <v>7154717</v>
+        <v>7154938</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,10 +1714,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119719039</v>
+        <v>119719037</v>
       </c>
       <c r="B12" t="n">
-        <v>91856</v>
+        <v>91862</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,25 +1726,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701788</v>
+        <v>701483</v>
       </c>
       <c r="R12" t="n">
-        <v>7154913</v>
+        <v>7155112</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 10862-2023 artfynd.xlsx
+++ b/artfynd/A 10862-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>56622841</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701834.1891125089</v>
+        <v>701834</v>
       </c>
       <c r="R2" t="n">
-        <v>7154851.98977902</v>
+        <v>7154852</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2014-07-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-07-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119719045</v>
+        <v>119719031</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701467</v>
+        <v>701907</v>
       </c>
       <c r="R3" t="n">
-        <v>7155124</v>
+        <v>7154864</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,37 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119719041</v>
+        <v>119719039</v>
       </c>
       <c r="B4" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>702065</v>
+        <v>701788</v>
       </c>
       <c r="R4" t="n">
-        <v>7154717</v>
+        <v>7154913</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119719031</v>
+        <v>119719043</v>
       </c>
       <c r="B5" t="n">
-        <v>89650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1098,19 +1068,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119719057</v>
+        <v>119719056</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1138,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701443</v>
+        <v>701769</v>
       </c>
       <c r="R6" t="n">
-        <v>7155186</v>
+        <v>7154938</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119719046</v>
+        <v>119719057</v>
       </c>
       <c r="B7" t="n">
-        <v>56524</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,38 +1176,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jenberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701374</v>
+        <v>701443</v>
       </c>
       <c r="R7" t="n">
-        <v>7155505</v>
+        <v>7155186</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,37 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119719034</v>
+        <v>119719037</v>
       </c>
       <c r="B8" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701751</v>
+        <v>701483</v>
       </c>
       <c r="R8" t="n">
-        <v>7154965</v>
+        <v>7155112</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,15 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119719043</v>
+        <v>119719040</v>
       </c>
       <c r="B9" t="n">
-        <v>92048</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1424,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1448,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701907</v>
+        <v>701361</v>
       </c>
       <c r="R9" t="n">
-        <v>7154864</v>
+        <v>7155081</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,15 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119719039</v>
+        <v>119719041</v>
       </c>
       <c r="B10" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1550,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701788</v>
+        <v>702065</v>
       </c>
       <c r="R10" t="n">
-        <v>7154913</v>
+        <v>7154717</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,37 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119719056</v>
+        <v>119719044</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1652,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701769</v>
+        <v>701739</v>
       </c>
       <c r="R11" t="n">
-        <v>7154938</v>
+        <v>7154993</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,37 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119719037</v>
+        <v>119719045</v>
       </c>
       <c r="B12" t="n">
-        <v>91862</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4365</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>701483</v>
+        <v>701467</v>
       </c>
       <c r="R12" t="n">
-        <v>7155112</v>
+        <v>7155124</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,6 +1744,204 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>119719047</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Jenberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>701783</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7154912</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>119719046</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Jenberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>701374</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7155505</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10862-2023 artfynd.xlsx
+++ b/artfynd/A 10862-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56622841</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719031</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719039</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719043</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719056</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719057</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719037</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719040</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719041</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719044</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719045</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719047</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1942,8 +2007,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719046</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>